--- a/untranslated/downloads/data-excel/5.2.1.2.xlsx
+++ b/untranslated/downloads/data-excel/5.2.1.2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B94CA44-6FD5-4E47-B493-08AAD639C5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>в отделы судебно-медицинской экспертизы</t>
   </si>
@@ -46,15 +47,6 @@
     <t>Число женщин, обратившихся по факту насилия в семье:</t>
   </si>
   <si>
-    <t>5.2.1.1a Число женщин,  обратившихся в органы здравоохранения от семейного насилия</t>
-  </si>
-  <si>
-    <t>5.2.1.1a Number of women contacting health authorities for domestic violence</t>
-  </si>
-  <si>
-    <t>5.2.1.1а Үй-бүлөлүк зомбулуктан саламаттык сактоо органдарына кайрылган аялдардын саны</t>
-  </si>
-  <si>
     <t>in forensic departments</t>
   </si>
   <si>
@@ -110,12 +102,21 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>5.2.1.2 Үй-бүлөлүк зомбулуктан саламаттык сактоо органдарына кайрылган аялдардын саны</t>
+  </si>
+  <si>
+    <t>5.2.1.2 Число женщин,  обратившихся в органы здравоохранения от семейного насилия</t>
+  </si>
+  <si>
+    <t>5.2.1.2 Number of women contacting health authorities for domestic violence</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -202,12 +203,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -216,28 +217,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -246,6 +241,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -525,8 +524,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="39.42578125" style="3" customWidth="1"/>
@@ -534,44 +533,33 @@
     <col min="8" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:17" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -589,93 +577,98 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
+      <c r="R3" s="17"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10">
+    <row r="4" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="8">
         <v>2010</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>2011</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="8">
         <v>2012</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>2013</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>2014</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>2015</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="8">
         <v>2016</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <v>2017</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="8">
         <v>2018</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="8">
         <v>2019</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="11">
         <v>2020</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="11">
         <v>2021</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="11">
         <v>2022</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="11">
         <v>2023</v>
       </c>
+      <c r="R4" s="18">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="15"/>
     </row>
-    <row r="6" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3">
         <v>1308</v>
@@ -707,28 +700,31 @@
       <c r="M6" s="3">
         <v>1764</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="12">
         <v>1713</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="12">
         <v>1860</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="12">
         <v>1373</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="12">
         <v>1209</v>
       </c>
+      <c r="R6" s="16">
+        <v>1423</v>
+      </c>
     </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3">
         <v>68</v>
@@ -757,39 +753,42 @@
       <c r="M7" s="3">
         <v>2</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="12">
         <v>1</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="12">
         <v>1</v>
       </c>
-      <c r="P7" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>27</v>
+      <c r="P7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="36" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="1:18" ht="36" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5">
         <v>401</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>581</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>509</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>508</v>
       </c>
       <c r="H8" s="3">
@@ -810,39 +809,42 @@
       <c r="M8" s="3">
         <v>539</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="12">
         <v>379</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="12">
         <v>510</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="12">
         <v>117</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="12">
         <v>373</v>
       </c>
+      <c r="R8" s="16">
+        <v>435</v>
+      </c>
     </row>
-    <row r="9" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:18" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5">
         <v>414</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>320</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>498</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>822</v>
       </c>
       <c r="H9" s="3">
@@ -863,39 +865,42 @@
       <c r="M9" s="3">
         <v>211</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="12">
         <v>180</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="12">
         <v>178</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="12">
         <v>154</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="12">
         <v>115</v>
       </c>
+      <c r="R9" s="16">
+        <v>158</v>
+      </c>
     </row>
-    <row r="10" spans="1:17" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="1:18" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7">
         <v>445</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>491</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>504</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>600</v>
       </c>
       <c r="H10" s="4">
@@ -916,17 +921,20 @@
       <c r="M10" s="4">
         <v>939</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="13">
         <v>798</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="13">
         <v>821</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="13">
         <v>885</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="13">
         <v>781</v>
+      </c>
+      <c r="R10" s="17">
+        <v>925</v>
       </c>
     </row>
   </sheetData>
